--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EHDSPUsageCategory</t>
+    <t>EHDSUsageCategory</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Categorizes the data processing as Primary Care or Secondary Use according to the EHDS.</t>
+    <t>Classifies the documented use of electronic health data as primary use or secondary use in the EHDS context.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>79</v>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-ehds-usage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
